--- a/files/港岛-赤柱-环角道7号、9号及11号.xlsx
+++ b/files/港岛-赤柱-环角道7号、9号及11号.xlsx
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2513</v>
+        <v>2542</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>176800000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>70354</v>
+        <v>69552</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>163540000</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>65078</v>
+        <v>64335</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2671</v>
+        <v>2705</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>168800000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>63197</v>
+        <v>62403</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>156140000</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>58458</v>
+        <v>57723</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
       <c r="B6" s="16" t="inlineStr">
         <is>
           <t>A号屋 (环角道7号)
-2671呎 (3房)
+2705呎 (3房)
 (已定价未售)
 $1.69亿
-$63,197/呎</t>
+$62,403/呎</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
       <c r="C7" s="16" t="inlineStr">
         <is>
           <t>B号屋 (环角道9号)
-2513呎 (3房)
+2542呎 (3房)
 (已定价未售)
 $1.77亿
-$70,354/呎</t>
+$69,552/呎</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr"/>
